--- a/WBS.xlsx
+++ b/WBS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/44cfc3f9855e2be0/바탕 화면/SW프로젝트/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9B0E31-D7C6-412A-B7DC-6722F7DD5AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{2C9B0E31-D7C6-412A-B7DC-6722F7DD5AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{191521C8-4655-4415-954C-E099F30EFFCB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D3BF391-664C-40C7-8D52-F7A1EA4D0CAD}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$O$3</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="330">
   <si>
     <t>단계</t>
   </si>
@@ -1099,6 +1096,14 @@
   </si>
   <si>
     <t>엔터티 도출 및 속성 정의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>실제 시작일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>실제 종료일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1412,10 +1417,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1453,7 +1462,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1559,7 +1568,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1701,7 +1710,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1709,17 +1718,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A1173E8-089C-45C4-9A5C-A654A0411D5B}">
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="2" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="29.125" customWidth="1"/>
     <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="11" max="12" width="9.375" customWidth="1"/>
+    <col min="11" max="14" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:15" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="24" t="s">
         <v>325</v>
       </c>
@@ -1735,8 +1744,10 @@
       <c r="K1" s="24"/>
       <c r="L1" s="24"/>
       <c r="M1" s="24"/>
-    </row>
-    <row r="2" spans="1:13" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+    </row>
+    <row r="2" spans="1:15" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>324</v>
       </c>
@@ -1752,8 +1763,10 @@
       <c r="K2" s="26"/>
       <c r="L2" s="26"/>
       <c r="M2" s="26"/>
-    </row>
-    <row r="3" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+    </row>
+    <row r="3" spans="1:15" ht="24" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1791,10 +1804,16 @@
         <v>10</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>12</v>
       </c>
@@ -1831,9 +1850,15 @@
       <c r="L4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22"/>
       <c r="B5" s="11" t="s">
         <v>21</v>
@@ -1868,9 +1893,15 @@
       <c r="L5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="15">
+        <v>46125</v>
+      </c>
+      <c r="N5" s="15">
+        <v>46127</v>
+      </c>
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1901,9 +1932,13 @@
       <c r="L6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="10">
+        <v>46126</v>
+      </c>
+      <c r="N6" s="10"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16" t="s">
@@ -1936,9 +1971,11 @@
       <c r="L7" s="19">
         <v>46129</v>
       </c>
-      <c r="M7" s="16"/>
-    </row>
-    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="16"/>
+    </row>
+    <row r="8" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22"/>
       <c r="B8" s="11" t="s">
         <v>29</v>
@@ -1973,9 +2010,15 @@
       <c r="L8" s="15">
         <v>46127</v>
       </c>
-      <c r="M8" s="12"/>
-    </row>
-    <row r="9" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="15">
+        <v>46125</v>
+      </c>
+      <c r="N8" s="15">
+        <v>46127</v>
+      </c>
+      <c r="O8" s="12"/>
+    </row>
+    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22"/>
       <c r="B9" s="11" t="s">
         <v>33</v>
@@ -2010,9 +2053,15 @@
       <c r="L9" s="15">
         <v>46126</v>
       </c>
-      <c r="M9" s="12"/>
-    </row>
-    <row r="10" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="15">
+        <v>46125</v>
+      </c>
+      <c r="N9" s="15">
+        <v>46127</v>
+      </c>
+      <c r="O9" s="12"/>
+    </row>
+    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2043,9 +2092,15 @@
       <c r="L10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="16"/>
-    </row>
-    <row r="11" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="19">
+        <v>46126</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" s="16"/>
+    </row>
+    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="s">
@@ -2078,9 +2133,11 @@
       <c r="L11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="7"/>
+    </row>
+    <row r="12" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -2111,9 +2168,11 @@
       <c r="L12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="16"/>
-    </row>
-    <row r="13" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="16"/>
+    </row>
+    <row r="13" spans="1:15" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>43</v>
       </c>
@@ -2150,9 +2209,11 @@
       <c r="L13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16" t="s">
@@ -2185,9 +2246,11 @@
       <c r="L14" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="M14" s="16"/>
-    </row>
-    <row r="15" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="16"/>
+    </row>
+    <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2218,9 +2281,11 @@
       <c r="L15" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="7"/>
+    </row>
+    <row r="16" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -2251,9 +2316,11 @@
       <c r="L16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="16"/>
-    </row>
-    <row r="17" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="16"/>
+    </row>
+    <row r="17" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2284,9 +2351,11 @@
       <c r="L17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="7"/>
+    </row>
+    <row r="18" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
@@ -2317,9 +2386,11 @@
       <c r="L18" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="M18" s="16"/>
-    </row>
-    <row r="19" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="16"/>
+    </row>
+    <row r="19" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2350,9 +2421,11 @@
       <c r="L19" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="7"/>
+    </row>
+    <row r="20" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20"/>
       <c r="B20" s="16"/>
       <c r="C20" s="16" t="s">
@@ -2385,9 +2458,11 @@
       <c r="L20" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="M20" s="16"/>
-    </row>
-    <row r="21" spans="1:13" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="16"/>
+    </row>
+    <row r="21" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20"/>
       <c r="B21" s="11" t="s">
         <v>69</v>
@@ -2422,9 +2497,11 @@
       <c r="L21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="M21" s="12"/>
-    </row>
-    <row r="22" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="12"/>
+    </row>
+    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="20"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16" t="s">
@@ -2457,9 +2534,11 @@
       <c r="L22" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="M22" s="16"/>
-    </row>
-    <row r="23" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="16"/>
+    </row>
+    <row r="23" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2490,9 +2569,11 @@
       <c r="L23" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="M23" s="7"/>
-    </row>
-    <row r="24" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="7"/>
+    </row>
+    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20"/>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -2523,9 +2604,11 @@
       <c r="L24" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="M24" s="16"/>
-    </row>
-    <row r="25" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="16"/>
+    </row>
+    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2556,9 +2639,11 @@
       <c r="L25" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="7"/>
+    </row>
+    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20"/>
       <c r="B26" s="16"/>
       <c r="C26" s="16" t="s">
@@ -2591,9 +2676,11 @@
       <c r="L26" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="M26" s="16"/>
-    </row>
-    <row r="27" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="16"/>
+    </row>
+    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7" t="s">
@@ -2626,9 +2713,11 @@
       <c r="L27" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:13" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="7"/>
+    </row>
+    <row r="28" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
         <v>86</v>
       </c>
@@ -2665,9 +2754,11 @@
       <c r="L28" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7" t="s">
@@ -2700,9 +2791,11 @@
       <c r="L29" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="M29" s="7"/>
-    </row>
-    <row r="30" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="7"/>
+    </row>
+    <row r="30" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20"/>
       <c r="B30" s="16"/>
       <c r="C30" s="16" t="s">
@@ -2735,9 +2828,11 @@
       <c r="L30" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="M30" s="16"/>
-    </row>
-    <row r="31" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="16"/>
+    </row>
+    <row r="31" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7" t="s">
@@ -2770,9 +2865,11 @@
       <c r="L31" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="M31" s="7"/>
-    </row>
-    <row r="32" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="7"/>
+    </row>
+    <row r="32" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16" t="s">
@@ -2805,9 +2902,11 @@
       <c r="L32" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="M32" s="16"/>
-    </row>
-    <row r="33" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="16"/>
+    </row>
+    <row r="33" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7" t="s">
@@ -2840,9 +2939,11 @@
       <c r="L33" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="7"/>
+    </row>
+    <row r="34" spans="1:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20"/>
       <c r="B34" s="11" t="s">
         <v>111</v>
@@ -2877,9 +2978,11 @@
       <c r="L34" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="M34" s="12"/>
-    </row>
-    <row r="35" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="12"/>
+    </row>
+    <row r="35" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7" t="s">
@@ -2912,9 +3015,11 @@
       <c r="L35" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="M35" s="7"/>
-    </row>
-    <row r="36" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="7"/>
+    </row>
+    <row r="36" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -2945,9 +3050,11 @@
       <c r="L36" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="M36" s="16"/>
-    </row>
-    <row r="37" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="16"/>
+    </row>
+    <row r="37" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -2978,9 +3085,11 @@
       <c r="L37" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="7"/>
+    </row>
+    <row r="38" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16" t="s">
@@ -3013,9 +3122,11 @@
       <c r="L38" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="M38" s="16"/>
-    </row>
-    <row r="39" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="16"/>
+    </row>
+    <row r="39" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -3046,9 +3157,11 @@
       <c r="L39" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="M39" s="7"/>
-    </row>
-    <row r="40" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="7"/>
+    </row>
+    <row r="40" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="20"/>
       <c r="B40" s="16"/>
       <c r="C40" s="16" t="s">
@@ -3081,9 +3194,11 @@
       <c r="L40" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="M40" s="16"/>
-    </row>
-    <row r="41" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="16"/>
+    </row>
+    <row r="41" spans="1:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20" t="s">
         <v>128</v>
       </c>
@@ -3120,9 +3235,11 @@
       <c r="L41" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20"/>
       <c r="B42" s="16"/>
       <c r="C42" s="16" t="s">
@@ -3155,9 +3272,11 @@
       <c r="L42" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="M42" s="16"/>
-    </row>
-    <row r="43" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="16"/>
+    </row>
+    <row r="43" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7" t="s">
@@ -3190,9 +3309,11 @@
       <c r="L43" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="M43" s="7"/>
-    </row>
-    <row r="44" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="7"/>
+    </row>
+    <row r="44" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20"/>
       <c r="B44" s="16"/>
       <c r="C44" s="16" t="s">
@@ -3225,9 +3346,11 @@
       <c r="L44" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="M44" s="16"/>
-    </row>
-    <row r="45" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="16"/>
+    </row>
+    <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7" t="s">
@@ -3260,9 +3383,11 @@
       <c r="L45" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="M45" s="7"/>
-    </row>
-    <row r="46" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="7"/>
+    </row>
+    <row r="46" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20"/>
       <c r="B46" s="11" t="s">
         <v>150</v>
@@ -3297,9 +3422,11 @@
       <c r="L46" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="M46" s="12"/>
-    </row>
-    <row r="47" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="12"/>
+    </row>
+    <row r="47" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7" t="s">
@@ -3332,9 +3459,11 @@
       <c r="L47" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="M47" s="7"/>
-    </row>
-    <row r="48" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="7"/>
+    </row>
+    <row r="48" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="20"/>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -3365,9 +3494,11 @@
       <c r="L48" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="M48" s="16"/>
-    </row>
-    <row r="49" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
+      <c r="O48" s="16"/>
+    </row>
+    <row r="49" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7" t="s">
@@ -3400,9 +3531,11 @@
       <c r="L49" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="M49" s="7"/>
-    </row>
-    <row r="50" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="7"/>
+    </row>
+    <row r="50" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20"/>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -3433,9 +3566,11 @@
       <c r="L50" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="M50" s="16"/>
-    </row>
-    <row r="51" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M50" s="19"/>
+      <c r="N50" s="19"/>
+      <c r="O50" s="16"/>
+    </row>
+    <row r="51" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7" t="s">
@@ -3468,9 +3603,11 @@
       <c r="L51" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="M51" s="7"/>
-    </row>
-    <row r="52" spans="1:13" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="7"/>
+    </row>
+    <row r="52" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="20" t="s">
         <v>167</v>
       </c>
@@ -3507,9 +3644,11 @@
       <c r="L52" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7" t="s">
@@ -3542,9 +3681,11 @@
       <c r="L53" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="M53" s="7"/>
-    </row>
-    <row r="54" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="7"/>
+    </row>
+    <row r="54" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="20"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16" t="s">
@@ -3577,9 +3718,11 @@
       <c r="L54" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="M54" s="16"/>
-    </row>
-    <row r="55" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M54" s="19"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="16"/>
+    </row>
+    <row r="55" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="20"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7" t="s">
@@ -3612,9 +3755,11 @@
       <c r="L55" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="M55" s="7"/>
-    </row>
-    <row r="56" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="7"/>
+    </row>
+    <row r="56" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="20"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16" t="s">
@@ -3647,9 +3792,11 @@
       <c r="L56" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="M56" s="16"/>
-    </row>
-    <row r="57" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M56" s="19"/>
+      <c r="N56" s="19"/>
+      <c r="O56" s="16"/>
+    </row>
+    <row r="57" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7" t="s">
@@ -3682,9 +3829,11 @@
       <c r="L57" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="M57" s="7"/>
-    </row>
-    <row r="58" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="7"/>
+    </row>
+    <row r="58" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="20"/>
       <c r="B58" s="16"/>
       <c r="C58" s="16" t="s">
@@ -3717,9 +3866,11 @@
       <c r="L58" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="M58" s="16"/>
-    </row>
-    <row r="59" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M58" s="19"/>
+      <c r="N58" s="19"/>
+      <c r="O58" s="16"/>
+    </row>
+    <row r="59" spans="1:15" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="20"/>
       <c r="B59" s="11" t="s">
         <v>191</v>
@@ -3754,9 +3905,11 @@
       <c r="L59" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="M59" s="12"/>
-    </row>
-    <row r="60" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="12"/>
+    </row>
+    <row r="60" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20"/>
       <c r="B60" s="16"/>
       <c r="C60" s="16" t="s">
@@ -3789,9 +3942,11 @@
       <c r="L60" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="M60" s="16"/>
-    </row>
-    <row r="61" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M60" s="19"/>
+      <c r="N60" s="19"/>
+      <c r="O60" s="16"/>
+    </row>
+    <row r="61" spans="1:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20"/>
       <c r="B61" s="11" t="s">
         <v>195</v>
@@ -3826,9 +3981,11 @@
       <c r="L61" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="M61" s="12"/>
-    </row>
-    <row r="62" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="12"/>
+    </row>
+    <row r="62" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16" t="s">
@@ -3861,9 +4018,11 @@
       <c r="L62" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="M62" s="16"/>
-    </row>
-    <row r="63" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M62" s="19"/>
+      <c r="N62" s="19"/>
+      <c r="O62" s="16"/>
+    </row>
+    <row r="63" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="20"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7" t="s">
@@ -3896,9 +4055,11 @@
       <c r="L63" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="M63" s="7"/>
-    </row>
-    <row r="64" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="7"/>
+    </row>
+    <row r="64" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="20"/>
       <c r="B64" s="16"/>
       <c r="C64" s="16" t="s">
@@ -3931,9 +4092,11 @@
       <c r="L64" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="M64" s="16"/>
-    </row>
-    <row r="65" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="16"/>
+    </row>
+    <row r="65" spans="1:15" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="20" t="s">
         <v>205</v>
       </c>
@@ -3970,9 +4133,11 @@
       <c r="L65" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="20"/>
       <c r="B66" s="16"/>
       <c r="C66" s="16" t="s">
@@ -4005,9 +4170,11 @@
       <c r="L66" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="M66" s="16"/>
-    </row>
-    <row r="67" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="16"/>
+    </row>
+    <row r="67" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="20"/>
       <c r="B67" s="11" t="s">
         <v>214</v>
@@ -4042,9 +4209,11 @@
       <c r="L67" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="M67" s="12"/>
-    </row>
-    <row r="68" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="12"/>
+    </row>
+    <row r="68" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="20"/>
       <c r="B68" s="16"/>
       <c r="C68" s="16" t="s">
@@ -4077,9 +4246,11 @@
       <c r="L68" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="M68" s="16"/>
-    </row>
-    <row r="69" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M68" s="19"/>
+      <c r="N68" s="19"/>
+      <c r="O68" s="16"/>
+    </row>
+    <row r="69" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7" t="s">
@@ -4112,9 +4283,11 @@
       <c r="L69" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="M69" s="7"/>
-    </row>
-    <row r="70" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="7"/>
+    </row>
+    <row r="70" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20"/>
       <c r="B70" s="11" t="s">
         <v>226</v>
@@ -4149,9 +4322,11 @@
       <c r="L70" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="M70" s="12"/>
-    </row>
-    <row r="71" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="12"/>
+    </row>
+    <row r="71" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7" t="s">
@@ -4184,9 +4359,11 @@
       <c r="L71" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="M71" s="7"/>
-    </row>
-    <row r="72" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="7"/>
+    </row>
+    <row r="72" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="20"/>
       <c r="B72" s="16"/>
       <c r="C72" s="16" t="s">
@@ -4219,9 +4396,11 @@
       <c r="L72" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="M72" s="16"/>
-    </row>
-    <row r="73" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M72" s="19"/>
+      <c r="N72" s="19"/>
+      <c r="O72" s="16"/>
+    </row>
+    <row r="73" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="20"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7" t="s">
@@ -4254,9 +4433,11 @@
       <c r="L73" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="M73" s="7"/>
-    </row>
-    <row r="74" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="7"/>
+    </row>
+    <row r="74" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="20"/>
       <c r="B74" s="16"/>
       <c r="C74" s="16" t="s">
@@ -4289,9 +4470,11 @@
       <c r="L74" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="M74" s="16"/>
-    </row>
-    <row r="75" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M74" s="19"/>
+      <c r="N74" s="19"/>
+      <c r="O74" s="16"/>
+    </row>
+    <row r="75" spans="1:15" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="20"/>
       <c r="B75" s="11" t="s">
         <v>241</v>
@@ -4326,9 +4509,11 @@
       <c r="L75" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="M75" s="12"/>
-    </row>
-    <row r="76" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="12"/>
+    </row>
+    <row r="76" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="20"/>
       <c r="B76" s="16"/>
       <c r="C76" s="16" t="s">
@@ -4361,9 +4546,11 @@
       <c r="L76" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="M76" s="16"/>
-    </row>
-    <row r="77" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M76" s="19"/>
+      <c r="N76" s="19"/>
+      <c r="O76" s="16"/>
+    </row>
+    <row r="77" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="20"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7" t="s">
@@ -4396,9 +4583,11 @@
       <c r="L77" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="M77" s="7"/>
-    </row>
-    <row r="78" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="7"/>
+    </row>
+    <row r="78" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="20"/>
       <c r="B78" s="16"/>
       <c r="C78" s="16" t="s">
@@ -4431,9 +4620,11 @@
       <c r="L78" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="M78" s="16"/>
-    </row>
-    <row r="79" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M78" s="19"/>
+      <c r="N78" s="19"/>
+      <c r="O78" s="16"/>
+    </row>
+    <row r="79" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="20"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7" t="s">
@@ -4466,9 +4657,11 @@
       <c r="L79" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="M79" s="7"/>
-    </row>
-    <row r="80" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="7"/>
+    </row>
+    <row r="80" spans="1:15" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="20" t="s">
         <v>255</v>
       </c>
@@ -4505,9 +4698,11 @@
       <c r="L80" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="M80" s="3"/>
-    </row>
-    <row r="81" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="3"/>
+    </row>
+    <row r="81" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="20"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7" t="s">
@@ -4540,9 +4735,11 @@
       <c r="L81" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="M81" s="7"/>
-    </row>
-    <row r="82" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="7"/>
+    </row>
+    <row r="82" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="20"/>
       <c r="B82" s="16"/>
       <c r="C82" s="16" t="s">
@@ -4575,9 +4772,11 @@
       <c r="L82" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="M82" s="16"/>
-    </row>
-    <row r="83" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M82" s="19"/>
+      <c r="N82" s="19"/>
+      <c r="O82" s="16"/>
+    </row>
+    <row r="83" spans="1:15" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="20"/>
       <c r="B83" s="11" t="s">
         <v>268</v>
@@ -4612,9 +4811,11 @@
       <c r="L83" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="M83" s="12"/>
-    </row>
-    <row r="84" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M83" s="15"/>
+      <c r="N83" s="15"/>
+      <c r="O83" s="12"/>
+    </row>
+    <row r="84" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="20"/>
       <c r="B84" s="16"/>
       <c r="C84" s="16" t="s">
@@ -4647,9 +4848,11 @@
       <c r="L84" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="M84" s="16"/>
-    </row>
-    <row r="85" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M84" s="19"/>
+      <c r="N84" s="19"/>
+      <c r="O84" s="16"/>
+    </row>
+    <row r="85" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="20"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7" t="s">
@@ -4682,9 +4885,11 @@
       <c r="L85" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="M85" s="7"/>
-    </row>
-    <row r="86" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M85" s="10"/>
+      <c r="N85" s="10"/>
+      <c r="O85" s="7"/>
+    </row>
+    <row r="86" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="20"/>
       <c r="B86" s="16"/>
       <c r="C86" s="16" t="s">
@@ -4717,9 +4922,11 @@
       <c r="L86" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="M86" s="16"/>
-    </row>
-    <row r="87" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M86" s="19"/>
+      <c r="N86" s="19"/>
+      <c r="O86" s="16"/>
+    </row>
+    <row r="87" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="20" t="s">
         <v>281</v>
       </c>
@@ -4756,9 +4963,11 @@
       <c r="L87" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="20"/>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -4789,9 +4998,11 @@
       <c r="L88" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="M88" s="16"/>
-    </row>
-    <row r="89" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M88" s="19"/>
+      <c r="N88" s="19"/>
+      <c r="O88" s="16"/>
+    </row>
+    <row r="89" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="20"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -4822,9 +5033,11 @@
       <c r="L89" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="M89" s="7"/>
-    </row>
-    <row r="90" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M89" s="10"/>
+      <c r="N89" s="10"/>
+      <c r="O89" s="7"/>
+    </row>
+    <row r="90" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="20"/>
       <c r="B90" s="16"/>
       <c r="C90" s="16"/>
@@ -4855,9 +5068,11 @@
       <c r="L90" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="M90" s="16"/>
-    </row>
-    <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M90" s="19"/>
+      <c r="N90" s="19"/>
+      <c r="O90" s="16"/>
+    </row>
+    <row r="91" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="20"/>
       <c r="B91" s="11" t="s">
         <v>296</v>
@@ -4892,9 +5107,11 @@
       <c r="L91" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="M91" s="12"/>
-    </row>
-    <row r="92" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M91" s="15"/>
+      <c r="N91" s="15"/>
+      <c r="O91" s="12"/>
+    </row>
+    <row r="92" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="20"/>
       <c r="B92" s="16"/>
       <c r="C92" s="16" t="s">
@@ -4927,9 +5144,11 @@
       <c r="L92" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="M92" s="16"/>
-    </row>
-    <row r="93" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M92" s="19"/>
+      <c r="N92" s="19"/>
+      <c r="O92" s="16"/>
+    </row>
+    <row r="93" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="20"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7" t="s">
@@ -4962,9 +5181,11 @@
       <c r="L93" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="M93" s="7"/>
-    </row>
-    <row r="94" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M93" s="10"/>
+      <c r="N93" s="10"/>
+      <c r="O93" s="7"/>
+    </row>
+    <row r="94" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="20"/>
       <c r="B94" s="16"/>
       <c r="C94" s="16" t="s">
@@ -4997,9 +5218,11 @@
       <c r="L94" s="19" t="s">
         <v>312</v>
       </c>
-      <c r="M94" s="16"/>
-    </row>
-    <row r="95" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M94" s="19"/>
+      <c r="N94" s="19"/>
+      <c r="O94" s="16"/>
+    </row>
+    <row r="95" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="20"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -5030,13 +5253,15 @@
       <c r="L95" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="M95" s="7"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="10"/>
+      <c r="O95" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M3" xr:uid="{0A1173E8-089C-45C4-9A5C-A654A0411D5B}"/>
+  <autoFilter ref="A3:O3" xr:uid="{0A1173E8-089C-45C4-9A5C-A654A0411D5B}"/>
   <mergeCells count="10">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A13:A27"/>
     <mergeCell ref="A28:A40"/>
     <mergeCell ref="A41:A51"/>
